--- a/reports/jobs_2026-09-30.xlsx
+++ b/reports/jobs_2026-09-30.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,7 +538,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -546,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careers.arm.com/job/bengaluru/design-engineer/33099/101349907152</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -561,104 +565,100 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Chargebee</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Product Launch and price new features without waiting on engineering</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chargebee.com/careers/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Chiang Mai 1 available jobs</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Chargebee</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Growth Test offers, run promotions and lift conversion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chargebee.com/careers/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -671,11 +671,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -683,12 +679,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -705,7 +701,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -730,7 +726,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -777,7 +773,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +795,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -812,7 +808,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -820,7 +820,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -855,7 +855,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -863,7 +867,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -885,7 +889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -898,11 +902,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -910,7 +910,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1031,7 +1031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1039,7 +1043,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1056,17 +1060,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1074,11 +1078,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,17 +1146,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1189,17 +1189,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Graphics Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1207,11 +1207,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Remote - India</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1219,12 +1215,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,17 +1232,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1256,7 +1252,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1266,12 +1262,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1283,12 +1279,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1301,11 +1297,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1313,12 +1305,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer-</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1330,17 +1322,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1348,11 +1340,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1360,12 +1348,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1377,17 +1365,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1397,7 +1385,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1407,12 +1395,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1424,17 +1412,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1444,7 +1432,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1454,12 +1442,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1476,7 +1464,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1491,7 +1479,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1501,7 +1489,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1523,7 +1511,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1536,7 +1524,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1544,7 +1536,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,7 +1558,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1591,7 +1583,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1613,7 +1605,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1628,7 +1620,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1638,7 +1630,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1660,12 +1652,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1673,11 +1665,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1685,7 +1673,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1707,12 +1695,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1732,7 +1720,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1754,7 +1742,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1779,7 +1767,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1801,12 +1789,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1826,7 +1814,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1843,17 +1831,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1863,7 +1851,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1873,12 +1861,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1890,12 +1878,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1908,7 +1896,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1916,12 +1908,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1933,17 +1925,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1951,7 +1943,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1959,12 +1955,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1976,12 +1972,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1994,7 +1990,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2062,17 +2062,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2080,11 +2080,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2092,12 +2088,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2109,12 +2105,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2127,11 +2123,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2139,12 +2131,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2156,12 +2148,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2174,11 +2166,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2186,12 +2174,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2203,17 +2191,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer (Java / .NET)</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2223,7 +2211,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, in</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2233,12 +2221,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2250,17 +2238,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2270,7 +2258,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2280,12 +2268,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2297,17 +2285,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2317,7 +2305,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2327,12 +2315,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2344,17 +2332,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Engineer (Java / .NET)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2362,7 +2350,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, in</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2370,12 +2362,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2387,12 +2379,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2405,7 +2397,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2413,12 +2409,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2430,17 +2426,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2450,7 +2446,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2460,12 +2456,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2477,17 +2473,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2495,11 +2491,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2507,12 +2499,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2524,12 +2516,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2550,12 +2542,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2567,12 +2559,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2587,7 +2579,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2597,12 +2589,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2614,17 +2606,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2632,7 +2624,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2640,12 +2636,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2657,17 +2653,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2683,12 +2679,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2700,17 +2696,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2720,7 +2716,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2730,12 +2726,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2747,17 +2743,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2765,11 +2761,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2777,12 +2769,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2794,12 +2786,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2812,11 +2804,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2824,12 +2812,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2846,7 +2834,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2861,7 +2849,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2871,7 +2859,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2893,7 +2881,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2918,7 +2906,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2935,17 +2923,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2953,7 +2941,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2961,12 +2953,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2978,17 +2970,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2998,7 +2990,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3008,12 +3000,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3025,17 +3017,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3045,7 +3037,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3055,12 +3047,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3072,17 +3064,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3090,11 +3082,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3102,12 +3090,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3119,17 +3107,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3137,7 +3125,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3145,12 +3137,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3162,17 +3154,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3182,7 +3174,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3192,12 +3184,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3209,17 +3201,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3229,7 +3221,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3239,12 +3231,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3256,12 +3248,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3274,11 +3266,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3286,12 +3274,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3308,12 +3296,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3323,7 +3311,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3333,7 +3321,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3355,12 +3343,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3370,7 +3358,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3380,7 +3368,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3397,17 +3385,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3417,7 +3405,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3427,12 +3415,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3444,12 +3432,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3462,7 +3450,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3470,12 +3462,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3487,17 +3479,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3505,7 +3497,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3513,12 +3509,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3530,17 +3526,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3548,7 +3544,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3573,17 +3573,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3591,11 +3591,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3603,12 +3599,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3620,17 +3616,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3638,11 +3634,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3650,12 +3642,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3667,12 +3659,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3693,12 +3685,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/integration-support-engineer/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3710,17 +3702,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure Transformation Engineer – IT</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3728,7 +3720,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3736,12 +3732,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3753,17 +3749,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3771,7 +3767,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3796,17 +3796,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3814,11 +3814,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3826,12 +3822,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sirion.ai/jobs/integration-support-engineer/</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3843,29 +3839,25 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Infrastructure Transformation Engineer – IT</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1–5 years</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3873,12 +3865,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3890,17 +3882,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3908,11 +3900,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3920,12 +3908,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3937,52 +3925,189 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Blogs Expert advice on design, engineering, AI and careers</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/insights/blog</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4060,6 +4185,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4119,15 +4247,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.indmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4136,18 +4284,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4156,18 +4304,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4176,26 +4324,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -4279,19 +4407,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OYO</t>
+          <t>PharmEasy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.oyorooms.com/careers/</t>
+          <t>https://pharmeasy.in/careers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
